--- a/data/stats/supp_tables/fallbio-anova.xlsx
+++ b/data/stats/supp_tables/fallbio-anova.xlsx
@@ -351,28 +351,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>rowname</t>
+          <t>model term</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Chisq</t>
+          <t>df1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Df</t>
+          <t>df2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Pr(&gt;Chisq)</t>
+          <t>F.ratio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p.value</t>
         </is>
       </c>
     </row>
@@ -383,13 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>75.69547566667627</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>3.655411774875454E-17</v>
+        <v>34.406</v>
+      </c>
+      <c r="E2">
+        <v>1.072078644043E-05</v>
       </c>
     </row>
     <row r="3">
@@ -399,13 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>117.1176684509099</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D3">
-        <v>2.203776855467864E-24</v>
+        <v>21.275</v>
+      </c>
+      <c r="E3">
+        <v>1.298616551855623E-11</v>
       </c>
     </row>
     <row r="4">
@@ -415,13 +426,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>13.82663936376563</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>0.0002004736056112453</v>
+        <v>12.012</v>
+      </c>
+      <c r="E4">
+        <v>0.04046915523106537</v>
       </c>
     </row>
     <row r="5">
@@ -431,13 +445,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>1048.011988531143</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D5">
-        <v>6.583119336299452E-230</v>
+        <v>718.66</v>
+      </c>
+      <c r="E5">
+        <v>1.096695961480291E-44</v>
       </c>
     </row>
     <row r="6">
@@ -447,13 +464,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>16.27148285329055</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D6">
-        <v>0.03865514525934911</v>
+        <v>2.128</v>
+      </c>
+      <c r="E6">
+        <v>0.04381406633795033</v>
       </c>
     </row>
     <row r="7">
@@ -463,45 +483,54 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.970895853823869</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>0.6154214711773173</v>
+        <v>0.195</v>
+      </c>
+      <c r="E7">
+        <v>0.8252401912349375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cctrt_id:straw_id</t>
+          <t>till_id:weayear</t>
         </is>
       </c>
       <c r="B8">
-        <v>3.730855144373879</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D8">
-        <v>0.4436541359025793</v>
+        <v>28.161</v>
+      </c>
+      <c r="E8">
+        <v>3.177324746758943E-10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>till_id:weayear</t>
+          <t>cctrt_id:straw_id</t>
         </is>
       </c>
       <c r="B9">
-        <v>30.07721081924318</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D9">
-        <v>2.94317885768203E-07</v>
+        <v>0.637</v>
+      </c>
+      <c r="E9">
+        <v>0.6380275714106085</v>
       </c>
     </row>
     <row r="10">
@@ -511,13 +540,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>84.09832088998913</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D10">
-        <v>2.356385470633119E-17</v>
+        <v>9.617000000000001</v>
+      </c>
+      <c r="E10">
+        <v>1.605077246173648E-06</v>
       </c>
     </row>
     <row r="11">
@@ -527,13 +559,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.2983172832555319</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D11">
-        <v>0.5849392610567719</v>
+        <v>3.454</v>
+      </c>
+      <c r="E11">
+        <v>0.06635163098685107</v>
       </c>
     </row>
     <row r="12">
@@ -543,13 +578,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>9.099819419695168</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D12">
-        <v>0.3339454624340568</v>
+        <v>0.95</v>
+      </c>
+      <c r="E12">
+        <v>0.4815284084200145</v>
       </c>
     </row>
     <row r="13">
@@ -559,13 +597,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>6.699907821691782</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="D13">
-        <v>0.5693290624920734</v>
+        <v>0.785</v>
+      </c>
+      <c r="E13">
+        <v>0.6167394568868007</v>
       </c>
     </row>
     <row r="14">
@@ -575,13 +616,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.442703730880971</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="D14">
-        <v>0.4860946769863515</v>
+        <v>0.483</v>
+      </c>
+      <c r="E14">
+        <v>0.6188122959229991</v>
       </c>
     </row>
     <row r="15">
@@ -591,13 +635,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>2.225265106751956</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D15">
-        <v>0.6944065188501145</v>
+        <v>0.607</v>
+      </c>
+      <c r="E15">
+        <v>0.6589321338087739</v>
       </c>
     </row>
     <row r="16">
@@ -607,13 +654,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>20.18755525868523</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="D16">
-        <v>0.009649285964804955</v>
+        <v>1.344</v>
+      </c>
+      <c r="E16">
+        <v>0.2323051152615896</v>
       </c>
     </row>
   </sheetData>
